--- a/docs/kiem-thu/Ket-qua-kiem-thu.xlsx
+++ b/docs/kiem-thu/Ket-qua-kiem-thu.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug log" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test case'!$A$1:$L$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test case'!$A$1:$L$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTA('Test case'!$A$2:$A$73)</f>
+        <f>COUNTA('Test case'!$A$2:$A$83)</f>
         <v/>
       </c>
     </row>
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>COUNTIF('Test case'!$I$2:$I$73,"Đạt")</f>
+        <f>COUNTIF('Test case'!$I$2:$I$83,"Đạt")</f>
         <v/>
       </c>
     </row>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF('Test case'!$I$2:$I$73,"Không đạt")</f>
+        <f>COUNTIF('Test case'!$I$2:$I$83,"Không đạt")</f>
         <v/>
       </c>
     </row>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF('Test case'!$I$2:$I$73,"Chưa test")</f>
+        <f>COUNTIF('Test case'!$I$2:$I$83,"Chưa test")</f>
         <v/>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>• Kết quả ngày 15/10/2026 lấy từ lần chạy: 25 unit test + 30 e2e test đều đạt.</t>
+          <t>• Kết quả ngày 15/10/2026 lấy từ lần chạy: 37 unit test + 48 e2e test đều đạt (sau Sprint 2).</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -749,7 +749,7 @@
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
-          <t>201, lịch sử có 2 bản ghi; UI hiển thị 'Đang chuẩn bị'. Phần thông báo push làm ở Sprint 2</t>
+          <t>201, lịch sử 2 bản ghi; người nhà nhận thông báo trong ứng dụng (notifications.e2e TC-01). Push FCM xem TC-31</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>204, sau đó xem ca trả 404. Phần thông báo kiểm lại ở Sprint 2</t>
+          <t>204, xem ca trả 404 và không nhận thông báo mới (notifications.e2e BR-05)</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
@@ -1203,23 +1203,35 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>Thủ công</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr"/>
+          <t>API e2e</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>test/notifications.e2e-spec.ts › TC-09</t>
+        </is>
+      </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>Cần push FCM (Sprint 2)</t>
+          <t>Thông báo được lưu, mở lại app thấy đủ và đánh dấu đã đọc; SSE tự kết nối lại. Push khi offline xem TC-31</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>Chưa test</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr"/>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-09.png</t>
+        </is>
+      </c>
       <c r="K10" s="7" t="inlineStr"/>
-      <c r="L10" s="7" t="inlineStr"/>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1955,10 +1967,578 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>TC-23</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>BR-05</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Không gửi thông báo cho người không còn liên kết</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Người nhà hủy liên kết; người lạ chưa liên kết → đổi trạng thái</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Cả hai không nhận thông báo</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>API e2e</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>test/notifications.e2e-spec.ts › BR-05</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>Danh sách thông báo của cả hai rỗng</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-23.png</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr"/>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>TC-24</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>FR-09</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Thông báo khi đổi lịch hoặc phòng</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Sửa tên ca → sửa giờ dự kiến</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Chỉ đổi lịch mới gửi 'Lịch phẫu thuật có thay đổi...'</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>API e2e + UI</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>test/notifications.e2e-spec.ts</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>Đúng 1 thông báo; UI hiện sau 113 ms</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-24.png</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>TC-25</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>FR-09, mục 11.1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Gửi push lỗi thì thử lại có giới hạn</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Giả lập FCM lỗi tạm thời / token hỏng</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Thử lại tối đa 3 lần, ghi FAILED + lỗi; xóa token hỏng</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>notifications.service.spec.ts; retry.spec.ts</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-25.png</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr"/>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>TC-26</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>FR-08, mục 11.2</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Cập nhật thời gian thực qua SSE</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Mở luồng sự kiện của người nhà đã liên kết và người lạ → đổi trạng thái</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>Chỉ người đã liên kết nhận sự kiện; màn hình đổi ngay</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>API e2e + UI</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>test/events.e2e-spec.ts</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>Người lạ không nhận; qua proxy web nhận ngay, UI cập nhật 113 ms</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-26.png</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr"/>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>TC-27</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>FR-12</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Quản trị viên tạo tài khoản nhân viên</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Tạo tài khoản STAFF → đăng nhập</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>Tài khoản mới đăng nhập được; không tạo được vai trò người nhà</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>API e2e + UI</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>test/admin.e2e-spec.ts</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>201, đăng nhập được; role FAMILY bị 400</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-27.png</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr"/>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>TC-28</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>FR-12</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Khóa tài khoản</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Khóa tài khoản đang đăng nhập; quản trị tự khóa mình</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Phiên cũ bị từ chối, đăng nhập lại bị từ chối; không tự khóa được</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>API e2e + UI</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>test/admin.e2e-spec.ts</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>401, 403; tự khóa trả 400</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-28.png</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr"/>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>TC-29</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>FR-12</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Sửa nội dung thông báo trong danh mục trạng thái</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Đổi nội dung 'Đang chuẩn bị' → đổi trạng thái một ca</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Người nhà nhận nội dung mới</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>API e2e</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>test/admin.e2e-spec.ts</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>Đúng nội dung mới</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-29.png</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr"/>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>TC-30</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>FR-11</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Xem nhật ký truy cập</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Lọc theo hành động, phân trang; người nhà mở chi tiết ca nhiều lần</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Kết quả đúng bộ lọc; lượt xem ghi 1 lần mỗi 5 phút</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>API e2e + UI</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>test/admin.e2e-spec.ts; linking.e2e-spec.ts › FR-11</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-30.png</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>TC-31</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>FR-09</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Push FCM thật tới điện thoại (cả khi app đóng/offline)</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Cấu hình Firebase → bật thông báo trong Cài đặt → đổi trạng thái</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Điện thoại hiện thông báo trong &lt; 5 giây</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Thủ công</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>Cần tạo dự án Firebase và điền khóa</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr"/>
+      <c r="K32" s="7" t="inlineStr"/>
+      <c r="L32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>TC-32</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Nhân viên gọi API quản trị</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Đăng nhập nhân viên → GET /admin/*</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Bị từ chối 403</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>API e2e</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>test/admin.e2e-spec.ts</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>403 cho cả 4 API</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-32.png</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr"/>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L23"/>
+  <autoFilter ref="A1:L33"/>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Đạt,Không đạt,Chưa test"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/kiem-thu/Ket-qua-kiem-thu.xlsx
+++ b/docs/kiem-thu/Ket-qua-kiem-thu.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug log" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test case'!$A$1:$L$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test case'!$A$1:$L$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,11 +38,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
       <sz val="10"/>
     </font>
     <font>
@@ -102,12 +97,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -115,9 +110,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -506,7 +498,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTA('Test case'!$A$2:$A$83)</f>
+        <f>COUNTA('Test case'!$A$2:$A$96)</f>
         <v/>
       </c>
     </row>
@@ -517,7 +509,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>COUNTIF('Test case'!$I$2:$I$83,"Đạt")</f>
+        <f>COUNTIF('Test case'!$I$2:$I$96,"Đạt")</f>
         <v/>
       </c>
     </row>
@@ -528,7 +520,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF('Test case'!$I$2:$I$83,"Không đạt")</f>
+        <f>COUNTIF('Test case'!$I$2:$I$96,"Không đạt")</f>
         <v/>
       </c>
     </row>
@@ -539,7 +531,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF('Test case'!$I$2:$I$83,"Chưa test")</f>
+        <f>COUNTIF('Test case'!$I$2:$I$96,"Chưa test")</f>
         <v/>
       </c>
     </row>
@@ -617,7 +609,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>• Kết quả ngày 15/10/2026 lấy từ lần chạy: 37 unit test + 48 e2e test đều đạt (sau Sprint 2).</t>
+          <t>• Kết quả ngày 15/10/2026 lấy từ lần chạy: 53 unit test + 56 e2e test đều đạt (sau Sprint 3); coverage gộp 94% statements.</t>
         </is>
       </c>
     </row>
@@ -632,7 +624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1264,20 +1256,32 @@
           <t>Hiệu năng (k6)</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>loadtest/tc10-nhieu-nguoi-nha.js</t>
+        </is>
+      </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>Làm ở buổi 8</t>
+          <t>Qua nginx: 0/6407 lỗi, thông báo p95 697 ms, màn hình p95 34 ms, 100/100 nhận đủ (xem BUG-10)</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Chưa test</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr"/>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-10.png</t>
+        </is>
+      </c>
       <c r="K11" s="7" t="inlineStr"/>
-      <c r="L11" s="7" t="inlineStr"/>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -2535,10 +2539,744 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>TC-33</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>NFR-03</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>500 người nhà cùng theo dõi một ca</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>k6 với FAMILIES=500 qua nginx, đổi 4 trạng thái</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Không lỗi; thông báo p95 &lt; 5 s; màn hình p95 &lt; 2 s</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>Hiệu năng (k6)</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>loadtest/tc10-nhieu-nguoi-nha.js</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>0/30841 lỗi (300 req/s); thông báo p95 1,04 s; màn hình p95 79 ms; 500/500 nhận đủ</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-33.png</t>
+        </is>
+      </c>
+      <c r="K34" s="7" t="inlineStr"/>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>TC-34</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>BUG-01</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Dò mật khẩu bằng cách đổi X-Forwarded-For</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>12 lần đăng nhập sai cùng tài khoản, mỗi lần một IP giả khác</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Bị chặn (429) từ lần thứ 11</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>Unit + thủ công</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>app-throttler.guard.spec.ts › BUG-01</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>401 ×10 rồi 429</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-34.png</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr"/>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>TC-35</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>BUG-11</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Né giới hạn đăng ký bằng token giả</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>12 lần đăng ký cùng IP, mỗi lần kèm Bearer ngẫu nhiên</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Bị chặn (429) từ lần thứ 11</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>Unit + thủ công (Docker)</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>app-throttler.guard.spec.ts › BUG-11</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>201 ×10 rồi 429</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-35.png</t>
+        </is>
+      </c>
+      <c r="K36" s="7" t="inlineStr"/>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>TC-36</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>BUG-02</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Liên kết với ca đã hoàn tất</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Cấp mã → hoàn tất ca → nhập mã</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Bị từ chối, báo ca đã kết thúc</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>API e2e</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>test/linking.e2e-spec.ts › BUG-02</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>400 'Ca phẫu thuật đã kết thúc'</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-36.png</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr"/>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>TC-37</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>BUG-03</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Liên kết hết hiệu lực sau khi ca kết thúc</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Hoàn tất ca → chạy thu hồi ngay và sau 25 giờ</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Ngay sau vẫn xem được; sau 24 giờ liên kết bị thu hồi</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>API e2e</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>test/linking.e2e-spec.ts › BUG-03</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>200 rồi 404, liên kết REVOKED</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-37.png</t>
+        </is>
+      </c>
+      <c r="K38" s="7" t="inlineStr"/>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>TC-38</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>BUG-04</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Thu hồi phiên khi đổi mật khẩu/vai trò</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>2 phiên → đổi mật khẩu; quản trị đổi vai trò tài khoản đang đăng nhập</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Phiên cũ bị từ chối; phiên vừa đổi nhận token mới</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>API e2e</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>auth.e2e-spec.ts, admin.e2e-spec.ts › BUG-04</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>401 cho phiên cũ; token mới dùng được</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-38.png</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr"/>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>TC-39</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>BUG-06</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Hết phiên khi mở link QR</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Thu hồi phiên → mở /lien-ket?code=... → bấm Theo dõi → đăng nhập lại</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>Về trang đăng nhập, rồi quay lại đúng trang với mã điền sẵn</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>UI thủ công (Docker)</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr"/>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi, liên kết thành công</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-39.png</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr"/>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>TC-40</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>BUG-07</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Đăng nhập với link chuyển hướng sai vai trò</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Mở /dang-nhap?next=/staff, đăng nhập bằng người nhà</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Về /theo-doi thay vì trang lỗi</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>UI thủ công (Docker)</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr"/>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>Về /theo-doi</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-40.png</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr"/>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>TC-41</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Mục 7</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Tự đăng xuất nhân viên khi không thao tác</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>Đăng nhập nhân viên, để yên 30 phút</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>Tự đăng xuất, trang đăng nhập báo phiên kết thúc</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>UI thủ công</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr"/>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>Chưa chờ đủ 30 phút để thử</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>Chưa test</t>
+        </is>
+      </c>
+      <c r="J42" s="7" t="inlineStr"/>
+      <c r="K42" s="7" t="inlineStr"/>
+      <c r="L42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>TC-42</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>NFR-11</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Sao lưu và khôi phục CSDL</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Khởi động stack Docker → lấy bản sao lưu → khôi phục vào CSDL tạm</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>Bản sao lưu đủ dữ liệu, khôi phục được</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>Thủ công (Docker)</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>deploy/backup.sh</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>12 bảng, 926 tài khoản, 4 ca (sau khi sửa BUG-12)</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-42.png</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr"/>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>TC-43</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>NFR-09</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Triển khai toàn hệ thống bằng Docker</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>docker compose up --build → seed → mở http://localhost:8080</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>5 container chạy; đăng nhập và các luồng chính hoạt động</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>Thủ công (Docker)</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>deploy/docker-compose.yml</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>postgres, api, web, nginx, backup đều chạy; API healthy</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J44" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-43.png</t>
+        </is>
+      </c>
+      <c r="K44" s="7" t="inlineStr"/>
+      <c r="L44" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>TC-44</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>BUG-08</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Ghi nhật ký đăng nhập sai</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Đăng nhập sai mật khẩu → đếm LOGIN_FAILED</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>Tăng thêm 1 bản ghi</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>API e2e</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>test/auth.e2e-spec.ts › BUG-08</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-44.png</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr"/>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>TC-45</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>BUG-09</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Header Authorization ưu tiên hơn cookie</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Gửi cả cookie người nhà và Bearer nhân viên</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>Xử lý theo Bearer</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>extract-token.spec.ts › BUG-09</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-45.png</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="inlineStr"/>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L33"/>
+  <autoFilter ref="A1:L46"/>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Đạt,Không đạt,Chưa test"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2552,7 +3290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2620,46 +3358,846 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>BUG-01</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>TC-05</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>(Ví dụ) Bộ đếm nhập sai mã lưu trong bộ nhớ, khởi động lại API thì mất</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>Nhập sai 4 lần → khởi động lại API → nhập sai tiếp</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>TC-34</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Giới hạn 10 lần đăng nhập/phút né được bằng header X-Forwarded-For giả; khi triển khai sau proxy thì mọi người dùng bị tính chung một IP</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Gửi 12 lần đăng nhập sai qua /api, mỗi lần một X-Forwarded-For khác → không bị chặn</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Đã sửa</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>ThienBao19</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>Đếm theo tài khoản bị thử (đăng nhập), theo người dùng (đã đăng nhập), theo IP (còn lại) — app-throttler.guard.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>BUG-02</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>TC-36</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Người nhà vẫn liên kết được với ca đã hoàn tất bằng mã cấp từ trước (trái mục 7)</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Cấp mã → đổi ca tới 'Đã hoàn tất' → người nhà nhập mã</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Đã sửa</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>ThienBao19</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Từ chối liên kết khi ca ở trạng thái cuối</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>BUG-03</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>TC-37</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Liên kết không tự hết hiệu lực sau khi ca kết thúc (mục 7)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Hoàn tất ca → nhiều ngày sau người nhà vẫn xem được ca</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Đã sửa</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>ThienBao19</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Tự thu hồi 24 giờ sau khi ca hoàn tất/bị hủy (quét mỗi 10 phút) — link-expiry.service.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>BUG-04</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>TC-38</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Đổi mật khẩu hoặc đổi vai trò không vô hiệu các phiên đăng nhập đang mở</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Đăng nhập trên 2 thiết bị → đổi mật khẩu ở thiết bị 1 → thiết bị 2 vẫn dùng được</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Đã sửa</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>ThienBao19</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>Thêm users.token_version; đổi mật khẩu/khóa/đổi vai trò tăng phiên bản; phiên hiện tại nhận token mới</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>BUG-05</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>TC-43</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Cookie Secure gắn cứng theo NODE_ENV: demo bằng http qua IP LAN không đăng nhập được; thời hạn cookie (8 giờ cố định) lệch với JWT</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Chạy production, mở http://&lt;IP LAN&gt;:8080 trên điện thoại → đăng nhập xong vẫn bị đá ra</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Đã sửa</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>ThienBao19</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>Biến COOKIE_SECURE và SESSION_HOURS dùng chung cho cookie và JWT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>BUG-06</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>TC-39</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Hết phiên khi mở link QR: đăng nhập lại thì mất mã; trang liên kết chỉ báo lỗi, không chuyển về đăng nhập</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Phiên bị thu hồi → mở /lien-ket?code=... → bấm Theo dõi</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Đã sửa</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>ThienBao19</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>apiFetch xử lý 401 tập trung, giữ cả query khi chuyển về trang đăng nhập</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>BUG-07</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>TC-40</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Đăng nhập với link chuyển hướng không đúng vai trò thì rơi vào trang lỗi 403</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Mở /dang-nhap?next=/staff → đăng nhập bằng tài khoản người nhà</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Đã sửa</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>ThienBao19</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Chỉ chuyển tới đường dẫn thuộc khu vực của vai trò</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>BUG-08</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>TC-44</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Không ghi nhật ký đăng nhập và đăng nhập sai (NFR-10)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Đăng nhập sai → xem nhật ký truy cập</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Đã sửa</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>ThienBao19</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>Ghi LOGIN, LOGIN_FAILED, CHANGE_PASSWORD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>BUG-09</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>TC-45</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>API ưu tiên cookie hơn header Authorization: client gửi token nhân viên nhưng bị xử lý như người nhà</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Thử tải k6: người nhà đăng nhập (cookie) → gọi API cấp mã bằng Bearer của nhân viên → 403</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Đã sửa</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>ThienBao19</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Header Authorization được ưu tiên — phát hiện nhờ k6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>BUG-10</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>TC-10</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Proxy /api của Next.js lỗi kết nối khi 100 người dùng đồng thời (3% request lỗi, thông báo trễ tới 32 giây)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Chạy k6 100 người nhà qua cổng 3000 của web</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Đã sửa</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>ThienBao19</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Triển khai đặt nginx phía trước: /api vào thẳng API → 0 lỗi với 500 người</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>BUG-11</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>TC-35</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Rate limit theo phiên chấp nhận cả token giả: gửi Bearer ngẫu nhiên là né được giới hạn đăng ký</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Đăng ký 12 lần cùng IP, mỗi lần kèm Authorization: Bearer &lt;chuỗi ngẫu nhiên&gt; → không bị chặn</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Đã sửa</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>ThienBao19</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Chỉ đếm theo người dùng khi token hợp lệ (đã ký đúng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>BUG-12</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>TC-42</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Bản sao lưu đầu tiên rỗng vì chạy trước khi API tạo bảng; bản tiếp theo phải chờ 24 giờ</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>docker compose up → mở bản sao lưu đầu tiên → khôi phục ra 0 bảng</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Đã sửa</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>ThienBao19</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Container backup chờ API healthy; đã thử khôi phục ra đủ 12 bảng</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>HC-01</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>TC-05, TC-26</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Bộ đếm nhập sai mã và bus sự kiện SSE lưu trong bộ nhớ: chỉ đúng khi chạy 1 instance API</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Chạy 2 instance API sau load balancer</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>Hạn chế đã biết</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr"/>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>15/10/2026</t>
-        </is>
-      </c>
-      <c r="I2" s="8" t="inlineStr"/>
-      <c r="J2" s="8" t="inlineStr">
-        <is>
-          <t>Chuyển sang Redis nếu chạy nhiều instance</t>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Mở rộng: chuyển sang Redis</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>HC-02</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>TC-30</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Chạy dev (không nginx) thì IP trong nhật ký lấy từ X-Forwarded-For do người dùng gửi nên có thể giả</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Gọi API qua cổng 3000 kèm X-Forwarded-For tự đặt</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Hạn chế đã biết</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Bản triển khai Docker có nginx ghi IP thật</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>HC-03</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>TC-14</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Đăng xuất chỉ xóa cookie trên thiết bị đó; token cũ nếu bị lộ còn dùng được tới hết phiên</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Sao chép token → đăng xuất → dùng lại token</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Hạn chế đã biết</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr"/>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Đổi mật khẩu để thu hồi mọi phiên</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>HC-04</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>TC-34</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Giới hạn đăng nhập theo tài khoản: người khác cố tình đăng nhập sai có thể làm tài khoản bị chặn 1 phút</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Đăng nhập sai 10 lần vào tài khoản của người khác</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Hạn chế đã biết</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Đánh đổi để chống dò mật khẩu</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>HC-05</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>TC-31</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Chưa thử push FCM trên điện thoại thật vì chưa có dự án Firebase</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Hạn chế đã biết</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Thông báo vẫn hiện trong ứng dụng qua SSE</t>
         </is>
       </c>
     </row>

--- a/docs/kiem-thu/Ket-qua-kiem-thu.xlsx
+++ b/docs/kiem-thu/Ket-qua-kiem-thu.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug log" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test case'!$A$1:$L$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test case'!$A$1:$L$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTA('Test case'!$A$2:$A$96)</f>
+        <f>COUNTA('Test case'!$A$2:$A$99)</f>
         <v/>
       </c>
     </row>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>COUNTIF('Test case'!$I$2:$I$96,"Đạt")</f>
+        <f>COUNTIF('Test case'!$I$2:$I$99,"Đạt")</f>
         <v/>
       </c>
     </row>
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF('Test case'!$I$2:$I$96,"Không đạt")</f>
+        <f>COUNTIF('Test case'!$I$2:$I$99,"Không đạt")</f>
         <v/>
       </c>
     </row>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF('Test case'!$I$2:$I$96,"Chưa test")</f>
+        <f>COUNTIF('Test case'!$I$2:$I$99,"Chưa test")</f>
         <v/>
       </c>
     </row>
@@ -609,7 +609,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>• Kết quả ngày 15/10/2026 lấy từ lần chạy: 53 unit test + 56 e2e test đều đạt (sau Sprint 3); coverage gộp 94% statements.</t>
+          <t>• Kết quả ngày 15/10/2026 lấy từ lần chạy: 53 unit + 57 e2e (Jest) + 23 kịch bản giao diện (Playwright) đều đạt; coverage gộp 94% statements.</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -751,7 +751,7 @@
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-01.png</t>
+          <t>anh/TC-01.png, anh/TC-01a-xac-nhan.png</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr"/>
@@ -809,7 +809,7 @@
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-02.png</t>
+          <t>anh/KQ-02-e2e-test.png</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr"/>
@@ -925,7 +925,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-04.png</t>
+          <t>anh/TC-04.png, anh/TC-04a-thu-hoi-ma.png</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr"/>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-06.png</t>
+          <t>anh/KQ-02-e2e-test.png</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr"/>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-07.png</t>
+          <t>anh/KQ-02-e2e-test.png</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr"/>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-08.png</t>
+          <t>anh/TC-08.png, anh/TC-08a-cai-dat.png</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr"/>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-09.png</t>
+          <t>anh/KQ-02-e2e-test.png</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr"/>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-10.png</t>
+          <t>anh/KQ-04-k6-100-nguoi-nha.png</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-11.png</t>
+          <t>anh/KQ-02-e2e-test.png</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr"/>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-13.png</t>
+          <t>anh/KQ-02-e2e-test.png</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr"/>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-14.png</t>
+          <t>anh/KQ-02-e2e-test.png</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr"/>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-15.png</t>
+          <t>anh/KQ-02-e2e-test.png</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr"/>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-17.png</t>
+          <t>anh/KQ-02-e2e-test.png</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr"/>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-18.png</t>
+          <t>anh/KQ-02-e2e-test.png</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr"/>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-19.png</t>
+          <t>anh/KQ-02-e2e-test.png</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr"/>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-20.png</t>
+          <t>anh/KQ-02-e2e-test.png</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr"/>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-21.png</t>
+          <t>anh/TC-26.png</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr"/>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-23.png</t>
+          <t>anh/KQ-02-e2e-test.png</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr"/>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-24.png</t>
+          <t>anh/TC-24.png, anh/TC-24a-sua-ca.png</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr"/>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-25.png</t>
+          <t>anh/KQ-01-unit-test.png</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr"/>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-32.png</t>
+          <t>anh/KQ-02-e2e-test.png</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-33.png</t>
+          <t>anh/KQ-05-k6-500-nguoi-nha.png</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr"/>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-34.png</t>
+          <t>anh/KQ-01-unit-test.png</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr"/>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-35.png</t>
+          <t>anh/KQ-01-unit-test.png</t>
         </is>
       </c>
       <c r="K36" s="7" t="inlineStr"/>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-36.png</t>
+          <t>anh/KQ-02-e2e-test.png</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr"/>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-37.png</t>
+          <t>anh/KQ-02-e2e-test.png</t>
         </is>
       </c>
       <c r="K38" s="7" t="inlineStr"/>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-38.png</t>
+          <t>anh/KQ-02-e2e-test.png</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr"/>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-39.png</t>
+          <t>anh/TC-39.png, anh/TC-39a-het-phien.png</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr"/>
@@ -3023,23 +3023,35 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>UI thủ công</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr"/>
+          <t>UI (Playwright)</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>e2e/tests/02-loi-va-phien.spec.ts › TC-41</t>
+        </is>
+      </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>Chưa chờ đủ 30 phút để thử</t>
+          <t>Tua đồng hồ 31 phút: tự về trang đăng nhập kèm thông báo; /auth/me trả 401</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>Chưa test</t>
-        </is>
-      </c>
-      <c r="J42" s="7" t="inlineStr"/>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-41.png</t>
+        </is>
+      </c>
       <c r="K42" s="7" t="inlineStr"/>
-      <c r="L42" s="7" t="inlineStr"/>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -3089,7 +3101,7 @@
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-42.png</t>
+          <t>anh/KQ-07-sao-luu-khoi-phuc.png</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr"/>
@@ -3147,7 +3159,7 @@
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-43.png</t>
+          <t>anh/KQ-06-trien-khai-docker.png</t>
         </is>
       </c>
       <c r="K44" s="7" t="inlineStr"/>
@@ -3263,7 +3275,7 @@
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-45.png</t>
+          <t>anh/KQ-01-unit-test.png</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr"/>
@@ -3273,10 +3285,184 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>TC-46</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>BUG-13, FR-04</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Nhân viên sửa giờ mổ trên giao diện</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Chi tiết ca → Sửa thông tin ca → đổi giờ → Lưu</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Lưu thành công; người nhà nhận thông báo đổi lịch</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>UI (Playwright)</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>e2e/tests/01-luong-chinh.spec.ts › TC-24</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-24a-sua-ca.png</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr"/>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>TC-47</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>BUG-15</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Giờ cập nhật của người nhà là giờ đổi trạng thái</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>Đổi trạng thái → sửa tên ca → người nhà xem chi tiết</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>Giờ hiển thị không đổi khi chỉ sửa tên ca</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>API e2e</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>test/linking.e2e-spec.ts › BUG-15</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>anh/KQ-02-e2e-test.png</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr"/>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>TC-48</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>BUG-16, NFR-11</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Sao lưu lỗi phải báo thất bại</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Chạy backup.sh --once với CSDL không tồn tại</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>Báo 'Sao lưu thất bại', không tạo file rỗng</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>Thủ công (Docker)</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>deploy/backup.sh</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi (số file trước/sau không đổi)</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>anh/KQ-07-sao-luu-khoi-phuc.png</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr"/>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L46"/>
+  <autoFilter ref="A1:L49"/>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Đạt,Không đạt,Chưa test"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3290,7 +3476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3984,66 +4170,74 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>HC-01</t>
+          <t>BUG-13</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>TC-05, TC-26</t>
+          <t>TC-46</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Bộ đếm nhập sai mã và bus sự kiện SSE lưu trong bộ nhớ: chỉ đúng khi chạy 1 instance API</t>
+          <t>Màn hình nhân viên thiếu chức năng sửa ca (tên, giờ dự kiến, phòng) dù FR-04 yêu cầu và API đã có</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Chạy 2 instance API sau load balancer</t>
+          <t>Mở chi tiết ca trên web nhân viên → không có chỗ đổi giờ mổ</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Thấp</t>
+          <t>Trung bình</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>Hạn chế đã biết</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr"/>
+          <t>Đã sửa</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>ThienBao19</t>
+        </is>
+      </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr"/>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>Mở rộng: chuyển sang Redis</t>
+          <t>Thêm form 'Sửa thông tin ca'; đổi giờ/phòng sẽ báo cho người nhà — phát hiện khi viết kịch bản Playwright</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>HC-02</t>
+          <t>BUG-14</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>TC-30</t>
+          <t>TC-44</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Chạy dev (không nginx) thì IP trong nhật ký lấy từ X-Forwarded-For do người dùng gửi nên có thể giả</t>
+          <t>Trang nhật ký truy cập không có nhãn và không lọc được các hành động mới (đăng nhập, đăng nhập sai, đổi mật khẩu)</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Gọi API qua cổng 3000 kèm X-Forwarded-For tự đặt</t>
+          <t>Quản trị → Nhật ký truy cập → ô Hành động không có 'Đăng nhập sai'; bảng hiện mã LOGIN_FAILED</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -4053,41 +4247,49 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Hạn chế đã biết</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr"/>
+          <t>Đã sửa</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>ThienBao19</t>
+        </is>
+      </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr"/>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>Bản triển khai Docker có nginx ghi IP thật</t>
+          <t>Bổ sung nhãn tiếng Việt cho LOGIN, LOGIN_FAILED, CHANGE_PASSWORD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>HC-03</t>
+          <t>BUG-15</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>TC-14</t>
+          <t>TC-47</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Đăng xuất chỉ xóa cookie trên thiết bị đó; token cũ nếu bị lộ còn dùng được tới hết phiên</t>
+          <t>Người nhà thấy 'Cập nhật lúc' là giờ sửa bản ghi ca, không phải giờ đổi trạng thái gần nhất (mục 12.1)</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Sao chép token → đăng xuất → dùng lại token</t>
+          <t>Nhân viên sửa tên ca → giờ 'Cập nhật lúc' của người nhà đổi theo dù trạng thái không đổi</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -4097,90 +4299,106 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>Hạn chế đã biết</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr"/>
+          <t>Đã sửa</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>ThienBao19</t>
+        </is>
+      </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr"/>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu để thu hồi mọi phiên</t>
+          <t>Lấy thời điểm của bản ghi lịch sử trạng thái mới nhất — phát hiện khi xem ảnh minh chứng</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>HC-04</t>
+          <t>BUG-16</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>TC-34</t>
+          <t>TC-48</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Giới hạn đăng nhập theo tài khoản: người khác cố tình đăng nhập sai có thể làm tài khoản bị chặn 1 phút</t>
+          <t>Script sao lưu báo 'Đã sao lưu' dù pg_dump lỗi và để lại file rỗng (mã thoát của pg_dump | gzip là của gzip); sau khi Docker khởi động lại, sao lưu chạy trước khi postgres sẵn sàng</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Đăng nhập sai 10 lần vào tài khoản của người khác</t>
+          <t>Khởi động lại Docker Desktop → log backup có 'Connection refused' nhưng vẫn ghi 'Đã sao lưu', file 20 byte</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Thấp</t>
+          <t>Trung bình</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Hạn chế đã biết</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr"/>
+          <t>Đã sửa</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>ThienBao19</t>
+        </is>
+      </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr"/>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>Đánh đổi để chống dò mật khẩu</t>
+          <t>Chờ pg_isready, kiểm tra mã thoát của pg_dump riêng; thêm --once và tiền tố theo stack — phát hiện khi chụp minh chứng</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>HC-05</t>
+          <t>HC-01</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>TC-31</t>
+          <t>TC-05, TC-26</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Chưa thử push FCM trên điện thoại thật vì chưa có dự án Firebase</t>
+          <t>Bộ đếm nhập sai mã và bus sự kiện SSE lưu trong bộ nhớ: chỉ đúng khi chạy 1 instance API</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Chạy 2 instance API sau load balancer</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Trung bình</t>
+          <t>Thấp</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -4197,7 +4415,227 @@
       <c r="I18" s="6" t="inlineStr"/>
       <c r="J18" s="6" t="inlineStr">
         <is>
+          <t>Mở rộng: chuyển sang Redis</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>HC-02</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>TC-30</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Chạy dev (không nginx) thì IP trong nhật ký lấy từ X-Forwarded-For do người dùng gửi nên có thể giả</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Gọi API qua cổng 3000 kèm X-Forwarded-For tự đặt</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Hạn chế đã biết</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr"/>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr"/>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>Bản triển khai Docker có nginx ghi IP thật</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>HC-03</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>TC-14</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Đăng xuất chỉ xóa cookie trên thiết bị đó; token cũ nếu bị lộ còn dùng được tới hết phiên</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Sao chép token → đăng xuất → dùng lại token</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Hạn chế đã biết</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Đổi mật khẩu để thu hồi mọi phiên</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>HC-04</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>TC-34</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Giới hạn đăng nhập theo tài khoản: người khác cố tình đăng nhập sai có thể làm tài khoản bị chặn 1 phút</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Đăng nhập sai 10 lần vào tài khoản của người khác</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Hạn chế đã biết</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Đánh đổi để chống dò mật khẩu</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>HC-05</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>TC-31</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Chưa thử push FCM trên điện thoại thật vì chưa có dự án Firebase</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Hạn chế đã biết</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr"/>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr"/>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
           <t>Thông báo vẫn hiện trong ứng dụng qua SSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>HC-06</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>KQ-01</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Jest báo 'worker failed to exit gracefully' khi chạy unit test song song trên Windows (do nạp Prisma/throttler), không ảnh hưởng kết quả</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>pnpm --filter @pt/api test</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Hạn chế đã biết</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr"/>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>Chạy tuần tự (--runInBand) và --detectOpenHandles không thấy rò rỉ</t>
         </is>
       </c>
     </row>

--- a/docs/kiem-thu/Ket-qua-kiem-thu.xlsx
+++ b/docs/kiem-thu/Ket-qua-kiem-thu.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug log" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test case'!$A$1:$L$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test case'!$A$1:$L$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTA('Test case'!$A$2:$A$99)</f>
+        <f>COUNTA('Test case'!$A$2:$A$105)</f>
         <v/>
       </c>
     </row>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>COUNTIF('Test case'!$I$2:$I$99,"Đạt")</f>
+        <f>COUNTIF('Test case'!$I$2:$I$105,"Đạt")</f>
         <v/>
       </c>
     </row>
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF('Test case'!$I$2:$I$99,"Không đạt")</f>
+        <f>COUNTIF('Test case'!$I$2:$I$105,"Không đạt")</f>
         <v/>
       </c>
     </row>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF('Test case'!$I$2:$I$99,"Chưa test")</f>
+        <f>COUNTIF('Test case'!$I$2:$I$105,"Chưa test")</f>
         <v/>
       </c>
     </row>
@@ -609,7 +609,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>• Kết quả ngày 15/10/2026 lấy từ lần chạy: 53 unit + 57 e2e (Jest) + 23 kịch bản giao diện (Playwright) đều đạt; coverage gộp 94% statements.</t>
+          <t>• Kết quả ngày 15/10/2026 lấy từ lần chạy: 55 unit + 56 e2e (Jest) + 22 kịch bản giao diện (Playwright) đều đạt; coverage gộp 94,5% statements (cập nhật 17/10/2026 sau khi đổi cách người nhà vào xem; 29/10/2026 thêm âm báo, chuông kết thúc, giữ phiên khi mở lại app).</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -832,17 +832,17 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Người nhà nhập mã hợp lệ</t>
+          <t>Người nhà vào xem bằng SĐT + họ tên + tên bệnh nhân</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Nhân viên cấp mã → người nhà nhập mã (chữ thường cũng được)</t>
+          <t>Nhân viên đăng ký người nhà (SĐT + họ tên) → người nhà nhập SĐT, họ tên mình, họ tên bệnh nhân</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Liên kết thành công, thấy bệnh nhân trong danh sách</t>
+          <t>Vào xem được ngay, không mật khẩu; thấy bệnh nhân với tên ẩn bớt</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>test/linking.e2e-spec.ts › TC-03</t>
+          <t>test/family-access.e2e-spec.ts › TC-03; e2e/tests/01-luong-chinh.spec.ts › TC-03</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>201; danh sách có ca, tên hiển thị 'N. V. An'</t>
+          <t>200; danh sách có ca, tên 'N. V. An'; giao diện vào thẳng /theo-doi</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-03.png</t>
+          <t>anh/TC-03.png, anh/TC-03a-nhap-thong-tin.png</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr"/>
@@ -885,37 +885,37 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>FR-06, BR-02</t>
+          <t>FR-07, BR-03</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Người nhà nhập mã hết hạn, đã thu hồi hoặc đã dùng</t>
+          <t>Thông tin không khớp với đăng ký</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Dùng lại mã đã dùng / mã bị thu hồi / mã quá hạn</t>
+          <t>Sai họ tên bệnh nhân / sai họ tên người nhà / SĐT chưa được đăng ký</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Báo lỗi, không tạo liên kết</t>
+          <t>Báo 'chưa khớp với đăng ký của bệnh viện', không vào được</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>API e2e</t>
+          <t>API e2e + UI</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>test/linking.e2e-spec.ts › TC-04 (3 test)</t>
+          <t>test/family-access.e2e-spec.ts › TC-04; e2e/tests/02-loi-va-phien.spec.ts › TC-04</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>400 với thông báo tương ứng cho cả 3 trường hợp</t>
+          <t>401 cho cả 3 trường hợp; giao diện hiện thông báo lỗi</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-04.png, anh/TC-04a-thu-hoi-ma.png</t>
+          <t>anh/TC-04.png</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr"/>
@@ -948,32 +948,32 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Nhập sai mã nhiều lần liên tiếp</t>
+          <t>Nhập sai nhiều lần liên tiếp</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Nhập sai mã 5 lần → lần 6</t>
+          <t>Nhập sai 5 lần với cùng một SĐT → lần 6</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Tạm khóa nhập mã trong một khoảng thời gian</t>
+          <t>Tạm khóa theo SĐT 15 phút</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>API e2e + Unit</t>
+          <t>API e2e + Unit + UI</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>test/linking.e2e-spec.ts › TC-05; attempt-limiter.spec.ts</t>
+          <t>test/family-access.e2e-spec.ts › TC-05; attempt-limiter.spec.ts; e2e/tests/02-loi-va-phien.spec.ts › TC-05</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>5 lần đầu 400, lần 6 trả 429 (khóa 15 phút)</t>
+          <t>401 ×5 rồi 429 'nhập sai quá nhiều lần'</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Người nhà gọi API xem ca chưa liên kết</t>
+          <t>Người nhà xem ca không được đăng ký cho mình</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>GET /my/surgeries/{id}, /surgeries/{id}/history, /surgeries/{id}</t>
+          <t>GET /my/surgeries/{id}, /surgeries/{id}/history, /surgeries/{id} của ca khác</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>test/linking.e2e-spec.ts › TC-06</t>
+          <t>test/family-access.e2e-spec.ts › TC-06</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -1122,32 +1122,32 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Thu hồi liên kết</t>
+          <t>Gỡ quyền theo dõi</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Người nhà bấm 'Ngừng theo dõi' → mở lại chi tiết ca</t>
+          <t>Nhân viên bấm 'Gỡ quyền' (hoặc người nhà 'Ngừng theo dõi') → người nhà mở lại ứng dụng</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Ngừng nhận thông báo và không xem được ca</t>
+          <t>Không xem được nữa; nhập lại thông tin bị từ chối</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>API e2e</t>
+          <t>API e2e + UI</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>test/linking.e2e-spec.ts › TC-08</t>
+          <t>test/family-access.e2e-spec.ts › TC-08; e2e/tests/01-luong-chinh.spec.ts › TC-08</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>204, xem ca trả 404 và không nhận thông báo mới (notifications.e2e BR-05)</t>
+          <t>401 'Phiên theo dõi đã kết thúc'; giao diện về /nguoi-nha, nhập lại báo 'chưa khớp'</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
@@ -1291,22 +1291,22 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-01, FR-07</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Đăng ký tài khoản người nhà</t>
+          <t>Nhân viên đăng ký người nhà cho ca</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Nhập họ tên, SĐT, mật khẩu ≥ 8 ký tự</t>
+          <t>Chi tiết ca → nhập SĐT + họ tên người nhà → Đăng ký</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Tạo tài khoản vai trò người nhà, không trả mật khẩu</t>
+          <t>Người nhà có trong danh sách của ca; SĐT của tài khoản nhân viên bị từ chối</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>test/auth.e2e-spec.ts</t>
+          <t>test/family-access.e2e-spec.ts › staff registers…; e2e/tests/01-luong-chinh.spec.ts › UC-01</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>201, role FAMILY; trùng SĐT trả 409</t>
+          <t>201, danh sách có người nhà; SĐT nhân viên trả 409</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>anh/KQ-02-e2e-test.png</t>
+          <t>anh/UC-01-dang-ky-nguoi-nha.png</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr"/>
@@ -1755,22 +1755,22 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>UC-01</t>
+          <t>Mục 7</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Cấp mã cho ca đã hoàn tất</t>
+          <t>Người nhà vẫn xem trong 24 giờ sau khi ca hoàn tất</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Đi đủ 5 trạng thái → cấp mã</t>
+          <t>Đi đủ 5 trạng thái → người nhà xem chi tiết ca</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Không cho tạo mã mới</t>
+          <t>Vẫn xem được kết quả</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>test/linking.e2e-spec.ts</t>
+          <t>test/family-access.e2e-spec.ts › BUG-03</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>200 ngay sau khi hoàn tất</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>test/linking.e2e-spec.ts › FR-08; mask-name.spec.ts</t>
+          <t>test/family-access.e2e-spec.ts › FR-08; mask-name.spec.ts</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -1925,33 +1925,37 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>FR-06, FR-07</t>
+          <t>FR-07, NFR-08</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Mở đường dẫn trong QR khi chưa đăng nhập</t>
+          <t>Gõ không dấu, hoa thường, SĐT có khoảng trắng hoặc +84</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Mở /lien-ket?code=... → đăng ký → quay lại</t>
+          <t>Nhập 'tran thi MAI', 'nguyen van an', '+84 901 234 567'</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Sau đăng ký quay về trang liên kết, mã được điền sẵn</t>
+          <t>Vẫn vào xem được</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>UI thủ công</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr"/>
+          <t>API e2e + UI</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>test/family-access.e2e-spec.ts › accepts names…; e2e/tests/02-loi-va-phien.spec.ts › gõ không dấu</t>
+        </is>
+      </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>Đúng như mong đợi</t>
+          <t>200; giao diện vào /theo-doi</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -1961,7 +1965,7 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-22.png</t>
+          <t>anh/TC-03b-khong-dau.png</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr"/>
@@ -1984,17 +1988,17 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Không gửi thông báo cho người không còn liên kết</t>
+          <t>Không gửi thông báo cho người không còn quyền</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Người nhà hủy liên kết; người lạ chưa liên kết → đổi trạng thái</t>
+          <t>Nhân viên gỡ quyền một người nhà; người nhà của ca khác → đổi trạng thái</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Cả hai không nhận thông báo</t>
+          <t>Không ai trong hai người nhận thông báo của ca</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -2009,7 +2013,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Danh sách thông báo của cả hai rỗng</t>
+          <t>Không có thông báo nào được tạo cho ca</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
@@ -2163,12 +2167,12 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Mở luồng sự kiện của người nhà đã liên kết và người lạ → đổi trạng thái</t>
+          <t>Mở luồng sự kiện của người nhà được đăng ký và của người nhà ca khác → đổi trạng thái</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Chỉ người đã liên kết nhận sự kiện; màn hình đổi ngay</t>
+          <t>Chỉ người được đăng ký nhận sự kiện; màn hình đổi ngay</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -2178,12 +2182,12 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>test/events.e2e-spec.ts</t>
+          <t>test/events.e2e-spec.ts; e2e/tests/01-luong-chinh.spec.ts › TC-26</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>Người lạ không nhận; qua proxy web nhận ngay, UI cập nhật 113 ms</t>
+          <t>Người ca khác không nhận; màn hình người nhà đổi trong vài trăm ms</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
@@ -2410,7 +2414,7 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>test/admin.e2e-spec.ts; linking.e2e-spec.ts › FR-11</t>
+          <t>test/admin.e2e-spec.ts; test/family-access.e2e-spec.ts › FR-11</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
@@ -2469,17 +2473,25 @@
       <c r="G32" s="6" t="inlineStr"/>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>Cần tạo dự án Firebase và điền khóa</t>
+          <t>iPhone (PWA thêm vào màn hình chính) đang tắt màn hình vẫn hiện thông báo 'Bệnh nhân đang được chuyển sang khu vực hồi sức' ngay sau khi đổi trạng thái; FCM trả SENT (dự án Firebase cdtn2-f0527)</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>Chưa test</t>
-        </is>
-      </c>
-      <c r="J32" s="7" t="inlineStr"/>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-31a-chuan-bi.png, anh/TC-31b-bat-dau.png, anh/TC-31c-hoi-suc.png, anh/TC-31d-hoan-tat.png</t>
+        </is>
+      </c>
       <c r="K32" s="7" t="inlineStr"/>
-      <c r="L32" s="7" t="inlineStr"/>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -2668,22 +2680,22 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Né giới hạn đăng ký bằng token giả</t>
+          <t>Né giới hạn tần suất bằng token giả</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>12 lần đăng ký cùng IP, mỗi lần kèm Bearer ngẫu nhiên</t>
+          <t>Gọi API công khai cùng IP, mỗi lần kèm Bearer ngẫu nhiên</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Bị chặn (429) từ lần thứ 11</t>
+          <t>Token giả bị tính theo IP, không né được giới hạn</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>Unit + thủ công (Docker)</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
@@ -2693,7 +2705,7 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>201 ×10 rồi 429</t>
+          <t>Đạt (lần kiểm thủ công 15/10 làm trên /auth/register, API này đã bỏ ngày 17/10)</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
@@ -2726,17 +2738,17 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Liên kết với ca đã hoàn tất</t>
+          <t>Không đăng ký thêm người nhà khi ca đã kết thúc</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Cấp mã → hoàn tất ca → nhập mã</t>
+          <t>Hoàn tất ca → nhân viên đăng ký người nhà</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Bị từ chối, báo ca đã kết thúc</t>
+          <t>Bị từ chối</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -2746,12 +2758,12 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>test/linking.e2e-spec.ts › BUG-02</t>
+          <t>test/family-access.e2e-spec.ts › UC-01 exception</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>400 'Ca phẫu thuật đã kết thúc'</t>
+          <t>409</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
@@ -2784,7 +2796,7 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Liên kết hết hiệu lực sau khi ca kết thúc</t>
+          <t>Quyền xem hết hiệu lực sau khi ca kết thúc</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -2794,7 +2806,7 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Ngay sau vẫn xem được; sau 24 giờ liên kết bị thu hồi</t>
+          <t>Ngay sau vẫn xem được; sau 24 giờ phiên người nhà kết thúc</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
@@ -2804,12 +2816,12 @@
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>test/linking.e2e-spec.ts › BUG-03</t>
+          <t>test/family-access.e2e-spec.ts › BUG-03</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>200 rồi 404, liên kết REVOKED</t>
+          <t>200 rồi 401, liên kết REVOKED</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
@@ -2895,33 +2907,37 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>BUG-06</t>
+          <t>FR-02</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Hết phiên khi mở link QR</t>
+          <t>Người nhà không có mật khẩu và không gọi được API nhân viên</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Thu hồi phiên → mở /lien-ket?code=... → bấm Theo dõi → đăng nhập lại</t>
+          <t>Người nhà gọi POST /patients và PUT /auth/password</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Về trang đăng nhập, rồi quay lại đúng trang với mã điền sẵn</t>
+          <t>Bị từ chối do sai vai trò</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>UI thủ công (Docker)</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr"/>
+          <t>API e2e</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>test/auth.e2e-spec.ts › forbids a family member…</t>
+        </is>
+      </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>Đúng như mong đợi, liên kết thành công</t>
+          <t>403, 403</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
@@ -2931,7 +2947,7 @@
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>anh/TC-39.png, anh/TC-39a-het-phien.png</t>
+          <t>anh/KQ-02-e2e-test.png</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr"/>
@@ -2949,33 +2965,37 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>BUG-07</t>
+          <t>FR-01</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Đăng nhập với link chuyển hướng sai vai trò</t>
+          <t>Người nhà dùng trang đăng nhập nhân viên</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Mở /dang-nhap?next=/staff, đăng nhập bằng người nhà</t>
+          <t>Nhập SĐT người nhà + mật khẩu bất kỳ ở /dang-nhap</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Về /theo-doi thay vì trang lỗi</t>
+          <t>Bị từ chối; trang có lối sang /nguoi-nha</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>UI thủ công (Docker)</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="inlineStr"/>
+          <t>API e2e + UI</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>test/auth.e2e-spec.ts › does not let a family member use password login; e2e/tests/02-loi-va-phien.spec.ts › TC-40</t>
+        </is>
+      </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>Về /theo-doi</t>
+          <t>401; trang hiện link 'Vào xem bằng số điện thoại'</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
@@ -3376,7 +3396,7 @@
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>test/linking.e2e-spec.ts › BUG-15</t>
+          <t>test/family-access.e2e-spec.ts › BUG-15</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
@@ -3459,10 +3479,358 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>TC-49</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Có sẵn 3 tài khoản nhân viên và 1 quản trị viên</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>Seed → đăng nhập nhanvien1/2/3@benhvien.test, admin@benhvien.test</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>Cả 4 tài khoản đăng nhập được, đúng vai trò</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>API e2e</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>test/auth.e2e-spec.ts › seeds 3 staff accounts…</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>200, role STAFF cho cả 3 nhân viên</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>anh/KQ-02-e2e-test.png</t>
+        </is>
+      </c>
+      <c r="K50" s="7" t="inlineStr"/>
+      <c r="L50" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>TC-50</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Bỏ tự đăng ký tài khoản</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>POST /auth/register</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>Không còn API tự đăng ký</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>API e2e</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>test/auth.e2e-spec.ts › no longer offers public self-registration</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>anh/KQ-02-e2e-test.png</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr"/>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>TC-51</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>FR-07</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Một SĐT được đăng ký cho 2 ca</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>Nhân viên đăng ký cùng SĐT vào 2 ca → người nhà vào xem 1 lần</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>Thấy cả 2 ca</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>API e2e</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>test/family-access.e2e-spec.ts › one phone registered for two surgeries…</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>Danh sách có đủ 2 ca</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J52" s="7" t="inlineStr">
+        <is>
+          <t>anh/KQ-02-e2e-test.png</t>
+        </is>
+      </c>
+      <c r="K52" s="7" t="inlineStr"/>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>TC-52</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Mở lại app khi phiên người nhà còn hạn</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Người nhà vào xem → đóng app → mở lại từ màn hình chính (trang chủ, /nguoi-nha)</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>Vào thẳng màn hình theo dõi, không phải nhập lại thông tin</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>UI (Playwright)</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>e2e/tests/07-am-bao-va-phien.spec.ts › TC-52</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>Chuyển thẳng tới /theo-doi; cookie phiên SameSite=Lax 7 ngày (sửa BUG-17)</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-52-mo-lai-app.png</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr"/>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>TC-53</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>FR-09</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Âm báo khi xong một giai đoạn</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>App người nhà đang mở → nhân viên chuyển 'Đã tiếp nhận' → 'Đang chuẩn bị'</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>Kêu một âm báo ngắn và rung nhẹ, không hiện chuông</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>UI (Playwright) + Unit</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>e2e/tests/07-am-bao-va-phien.spec.ts › TC-53; notifications.service.spec.ts</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>2 nốt âm báo + 1 lần rung; thông báo đẩy mang alert=stage</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-53-am-bao-giai-doan.png</t>
+        </is>
+      </c>
+      <c r="K54" s="7" t="inlineStr"/>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>TC-54</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>FR-09</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Chuông reo khi ca kết thúc</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>App người nhà đang mở → nhân viên chuyển ca tới 'Đã hoàn tất' → bấm 'Tắt chuông'</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Chuông reo và rung lặp lại tới khi người nhà bấm tắt</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>UI (Playwright) + Unit</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>e2e/tests/07-am-bao-va-phien.spec.ts › TC-54</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>Hiện bảng 'Ca phẫu thuật đã hoàn tất', chuông lặp mỗi 1,6 giây, dừng hẳn sau khi bấm tắt; push alert=final giữ thông báo trên màn hình (requireInteraction)</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>anh/TC-54-chuong-ket-thuc.png</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr"/>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L49"/>
+  <autoFilter ref="A1:L55"/>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Đạt,Không đạt,Chưa test"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3476,7 +3844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3643,7 +4011,7 @@
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
-          <t>Từ chối liên kết khi ca ở trạng thái cuối</t>
+          <t>Từ chối liên kết khi ca ở trạng thái cuối — Luồng mã/QR đã thay bằng nhân viên đăng ký người nhà (17/10/2026)</t>
         </is>
       </c>
     </row>
@@ -3851,7 +4219,7 @@
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>apiFetch xử lý 401 tập trung, giữ cả query khi chuyển về trang đăng nhập</t>
+          <t>apiFetch xử lý 401 tập trung, giữ cả query khi chuyển về trang đăng nhập — Luồng mã/QR đã thay bằng nhân viên đăng ký người nhà (17/10/2026)</t>
         </is>
       </c>
     </row>
@@ -4378,66 +4746,74 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>HC-01</t>
+          <t>BUG-17</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>TC-05, TC-26</t>
+          <t>TC-52</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Bộ đếm nhập sai mã và bus sự kiện SSE lưu trong bộ nhớ: chỉ đúng khi chạy 1 instance API</t>
+          <t>Người nhà mở lại app (PWA trên iPhone) thì phải nhập lại thông tin dù phiên 7 ngày vẫn còn — ảnh anh/BUG-17-mo-lai-app-mat-phien.png</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Chạy 2 instance API sau load balancer</t>
+          <t>Thêm app vào màn hình chính → vào xem → đóng app → mở lại: hiện trang chủ/form nhập thông tin</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Thấp</t>
+          <t>Cao</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>Hạn chế đã biết</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr"/>
+          <t>Đã sửa</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>ThienBao19</t>
+        </is>
+      </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr"/>
+          <t>29/10/2026</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>Mở rộng: chuyển sang Redis</t>
+          <t>Trang chủ và /nguoi-nha kiểm tra phiên (GET /auth/me) rồi chuyển thẳng tới trang theo dõi; cookie phiên đổi SameSite=Strict → Lax để vẫn được gửi khi mở app từ màn hình chính hoặc bấm vào thông báo — người dùng phát hiện khi thử trên điện thoại</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>HC-02</t>
+          <t>HC-01</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>TC-30</t>
+          <t>TC-05, TC-26</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Chạy dev (không nginx) thì IP trong nhật ký lấy từ X-Forwarded-For do người dùng gửi nên có thể giả</t>
+          <t>Bộ đếm nhập sai mã và bus sự kiện SSE lưu trong bộ nhớ: chỉ đúng khi chạy 1 instance API</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Gọi API qua cổng 3000 kèm X-Forwarded-For tự đặt</t>
+          <t>Chạy 2 instance API sau load balancer</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -4459,29 +4835,29 @@
       <c r="I19" s="6" t="inlineStr"/>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>Bản triển khai Docker có nginx ghi IP thật</t>
+          <t>Mở rộng: chuyển sang Redis</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>HC-03</t>
+          <t>HC-02</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>TC-14</t>
+          <t>TC-30</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Đăng xuất chỉ xóa cookie trên thiết bị đó; token cũ nếu bị lộ còn dùng được tới hết phiên</t>
+          <t>Chạy dev (không nginx) thì IP trong nhật ký lấy từ X-Forwarded-For do người dùng gửi nên có thể giả</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Sao chép token → đăng xuất → dùng lại token</t>
+          <t>Gọi API qua cổng 3000 kèm X-Forwarded-For tự đặt</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -4503,29 +4879,29 @@
       <c r="I20" s="6" t="inlineStr"/>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu để thu hồi mọi phiên</t>
+          <t>Bản triển khai Docker có nginx ghi IP thật</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>HC-04</t>
+          <t>HC-03</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>TC-34</t>
+          <t>TC-14</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Giới hạn đăng nhập theo tài khoản: người khác cố tình đăng nhập sai có thể làm tài khoản bị chặn 1 phút</t>
+          <t>Đăng xuất chỉ xóa cookie trên thiết bị đó; token cũ nếu bị lộ còn dùng được tới hết phiên</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Đăng nhập sai 10 lần vào tài khoản của người khác</t>
+          <t>Sao chép token → đăng xuất → dùng lại token</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -4547,34 +4923,34 @@
       <c r="I21" s="6" t="inlineStr"/>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>Đánh đổi để chống dò mật khẩu</t>
+          <t>Đổi mật khẩu để thu hồi mọi phiên</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>HC-05</t>
+          <t>HC-04</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>TC-31</t>
+          <t>TC-34</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Chưa thử push FCM trên điện thoại thật vì chưa có dự án Firebase</t>
+          <t>Giới hạn đăng nhập theo tài khoản: người khác cố tình đăng nhập sai có thể làm tài khoản bị chặn 1 phút</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Đăng nhập sai 10 lần vào tài khoản của người khác</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Trung bình</t>
+          <t>Thấp</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -4591,29 +4967,29 @@
       <c r="I22" s="6" t="inlineStr"/>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>Thông báo vẫn hiện trong ứng dụng qua SSE</t>
+          <t>Đánh đổi để chống dò mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>HC-06</t>
+          <t>HC-05</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>KQ-01</t>
+          <t>TC-31, TC-54</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Jest báo 'worker failed to exit gracefully' khi chạy unit test song song trên Windows (do nạp Prisma/throttler), không ảnh hưởng kết quả</t>
+          <t>iPhone không cho web rung máy; khi app đang đóng hệ điều hành chỉ phát âm thông báo mặc định một lần, chuông lặp chỉ có khi app đang mở</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>pnpm --filter @pt/api test</t>
+          <t>Tắt app trên iPhone → nhân viên chuyển ca sang 'Đã hoàn tất'</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -4629,13 +5005,101 @@
       <c r="G23" s="6" t="inlineStr"/>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr"/>
       <c r="J23" s="6" t="inlineStr">
         <is>
+          <t>Giới hạn của web push trên iOS; Android vẫn rung dài và giữ thông báo tới khi người dùng tắt</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>HC-06</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>KQ-01</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Jest báo 'worker failed to exit gracefully' khi chạy unit test song song trên Windows (do nạp Prisma/throttler), không ảnh hưởng kết quả</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>pnpm --filter @pt/api test</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Hạn chế đã biết</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr"/>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
           <t>Chạy tuần tự (--runInBand) và --detectOpenHandles không thấy rò rỉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>HC-07</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>TC-03, TC-05</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Người nhà vào xem không cần mật khẩu: ai biết đúng SĐT, họ tên người nhà và họ tên bệnh nhân đã được đăng ký thì xem được</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Nhập đúng 3 thông tin của một người nhà đã được đăng ký</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Hạn chế đã biết</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr"/>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>Theo yêu cầu (không mật khẩu, không xác nhận). Giảm thiểu: chỉ người nhân viên đăng ký mới vào được, khóa 5 lần sai/15 phút theo SĐT, phiên hết khi ca kết thúc, nhật ký FAMILY_ACCESS</t>
         </is>
       </c>
     </row>

--- a/docs/kiem-thu/Ket-qua-kiem-thu.xlsx
+++ b/docs/kiem-thu/Ket-qua-kiem-thu.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug log" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test case'!$A$1:$L$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test case'!$A$1:$L$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTA('Test case'!$A$2:$A$105)</f>
+        <f>COUNTA('Test case'!$A$2:$A$106)</f>
         <v/>
       </c>
     </row>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>COUNTIF('Test case'!$I$2:$I$105,"Đạt")</f>
+        <f>COUNTIF('Test case'!$I$2:$I$106,"Đạt")</f>
         <v/>
       </c>
     </row>
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF('Test case'!$I$2:$I$105,"Không đạt")</f>
+        <f>COUNTIF('Test case'!$I$2:$I$106,"Không đạt")</f>
         <v/>
       </c>
     </row>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF('Test case'!$I$2:$I$105,"Chưa test")</f>
+        <f>COUNTIF('Test case'!$I$2:$I$106,"Chưa test")</f>
         <v/>
       </c>
     </row>
@@ -624,7 +624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3827,10 +3827,68 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>TC-55</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>FR-09</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Đổi người nhà trên cùng điện thoại vẫn nhận push</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Điện thoại đã bật thông báo cho người nhà A → người nhà B vào xem trên cùng máy → nhân viên đổi trạng thái ca của B, tắt màn hình</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>Thông báo của B hiện trên màn hình khóa</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>API e2e + Thủ công</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>test/notifications.e2e-spec.ts › TC-55</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>Mở app thì token chuyển sang B; 4 thông báo ca thử 31/10 đều SENT tới iPhone</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="J56" s="7" t="inlineStr">
+        <is>
+          <t>anh/KQ-02-e2e-test.png</t>
+        </is>
+      </c>
+      <c r="K56" s="7" t="inlineStr"/>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L55"/>
+  <autoFilter ref="A1:L56"/>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Đạt,Không đạt,Chưa test"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3844,7 +3902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4798,66 +4856,74 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>HC-01</t>
+          <t>BUG-18</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>TC-05, TC-26</t>
+          <t>TC-55</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Bộ đếm nhập sai mã và bus sự kiện SSE lưu trong bộ nhớ: chỉ đúng khi chạy 1 instance API</t>
+          <t>Người nhà thứ hai vào xem trên điện thoại đã bật thông báo thì không nhận push (bị ghi SKIPPED)</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Chạy 2 instance API sau load balancer</t>
+          <t>Bật thông báo khi vào bằng người nhà A → vào bằng người nhà B trên cùng máy → đổi trạng thái ca của B</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Thấp</t>
+          <t>Cao</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Hạn chế đã biết</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr"/>
+          <t>Đã sửa</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>ThienBao19</t>
+        </is>
+      </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr"/>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>Mở rộng: chuyển sang Redis</t>
+          <t>Token thiết bị vẫn gắn với A vì nút Cài đặt hiện 'đang bật' nên không đăng ký lại; nay mỗi lần mở app tự đăng ký lại token cho người đang vào xem — người dùng phát hiện khi thử trên điện thoại</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>HC-02</t>
+          <t>HC-01</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>TC-30</t>
+          <t>TC-05, TC-26</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Chạy dev (không nginx) thì IP trong nhật ký lấy từ X-Forwarded-For do người dùng gửi nên có thể giả</t>
+          <t>Bộ đếm nhập sai mã và bus sự kiện SSE lưu trong bộ nhớ: chỉ đúng khi chạy 1 instance API</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Gọi API qua cổng 3000 kèm X-Forwarded-For tự đặt</t>
+          <t>Chạy 2 instance API sau load balancer</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -4879,29 +4945,29 @@
       <c r="I20" s="6" t="inlineStr"/>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>Bản triển khai Docker có nginx ghi IP thật</t>
+          <t>Mở rộng: chuyển sang Redis</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>HC-03</t>
+          <t>HC-02</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>TC-14</t>
+          <t>TC-30</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Đăng xuất chỉ xóa cookie trên thiết bị đó; token cũ nếu bị lộ còn dùng được tới hết phiên</t>
+          <t>Chạy dev (không nginx) thì IP trong nhật ký lấy từ X-Forwarded-For do người dùng gửi nên có thể giả</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Sao chép token → đăng xuất → dùng lại token</t>
+          <t>Gọi API qua cổng 3000 kèm X-Forwarded-For tự đặt</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -4923,29 +4989,29 @@
       <c r="I21" s="6" t="inlineStr"/>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu để thu hồi mọi phiên</t>
+          <t>Bản triển khai Docker có nginx ghi IP thật</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>HC-04</t>
+          <t>HC-03</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>TC-34</t>
+          <t>TC-14</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Giới hạn đăng nhập theo tài khoản: người khác cố tình đăng nhập sai có thể làm tài khoản bị chặn 1 phút</t>
+          <t>Đăng xuất chỉ xóa cookie trên thiết bị đó; token cũ nếu bị lộ còn dùng được tới hết phiên</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Đăng nhập sai 10 lần vào tài khoản của người khác</t>
+          <t>Sao chép token → đăng xuất → dùng lại token</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -4967,29 +5033,29 @@
       <c r="I22" s="6" t="inlineStr"/>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>Đánh đổi để chống dò mật khẩu</t>
+          <t>Đổi mật khẩu để thu hồi mọi phiên</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>HC-05</t>
+          <t>HC-04</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>TC-31, TC-54</t>
+          <t>TC-34</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>iPhone không cho web rung máy; khi app đang đóng hệ điều hành chỉ phát âm thông báo mặc định một lần, chuông lặp chỉ có khi app đang mở</t>
+          <t>Giới hạn đăng nhập theo tài khoản: người khác cố tình đăng nhập sai có thể làm tài khoản bị chặn 1 phút</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Tắt app trên iPhone → nhân viên chuyển ca sang 'Đã hoàn tất'</t>
+          <t>Đăng nhập sai 10 lần vào tài khoản của người khác</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -5011,29 +5077,29 @@
       <c r="I23" s="6" t="inlineStr"/>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>Giới hạn của web push trên iOS; Android vẫn rung dài và giữ thông báo tới khi người dùng tắt</t>
+          <t>Đánh đổi để chống dò mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>HC-06</t>
+          <t>HC-05</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>KQ-01</t>
+          <t>TC-31, TC-54</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Jest báo 'worker failed to exit gracefully' khi chạy unit test song song trên Windows (do nạp Prisma/throttler), không ảnh hưởng kết quả</t>
+          <t>iPhone không cho web rung máy; khi app đang đóng hệ điều hành chỉ phát âm thông báo mặc định một lần, chuông lặp chỉ có khi app đang mở</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>pnpm --filter @pt/api test</t>
+          <t>Tắt app trên iPhone → nhân viên chuyển ca sang 'Đã hoàn tất'</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -5049,40 +5115,40 @@
       <c r="G24" s="6" t="inlineStr"/>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr"/>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>Chạy tuần tự (--runInBand) và --detectOpenHandles không thấy rò rỉ</t>
+          <t>Giới hạn của web push trên iOS; Android vẫn rung dài và giữ thông báo tới khi người dùng tắt</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>HC-07</t>
+          <t>HC-06</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>TC-03, TC-05</t>
+          <t>KQ-01</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Người nhà vào xem không cần mật khẩu: ai biết đúng SĐT, họ tên người nhà và họ tên bệnh nhân đã được đăng ký thì xem được</t>
+          <t>Jest báo 'worker failed to exit gracefully' khi chạy unit test song song trên Windows (do nạp Prisma/throttler), không ảnh hưởng kết quả</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Nhập đúng 3 thông tin của một người nhà đã được đăng ký</t>
+          <t>pnpm --filter @pt/api test</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Trung bình</t>
+          <t>Thấp</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -5093,11 +5159,55 @@
       <c r="G25" s="6" t="inlineStr"/>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>17/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr"/>
       <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>Chạy tuần tự (--runInBand) và --detectOpenHandles không thấy rò rỉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>HC-07</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>TC-03, TC-05</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Người nhà vào xem không cần mật khẩu: ai biết đúng SĐT, họ tên người nhà và họ tên bệnh nhân đã được đăng ký thì xem được</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Nhập đúng 3 thông tin của một người nhà đã được đăng ký</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Hạn chế đã biết</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr"/>
+      <c r="J26" s="6" t="inlineStr">
         <is>
           <t>Theo yêu cầu (không mật khẩu, không xác nhận). Giảm thiểu: chỉ người nhân viên đăng ký mới vào được, khóa 5 lần sai/15 phút theo SĐT, phiên hết khi ca kết thúc, nhật ký FAMILY_ACCESS</t>
         </is>
